--- a/src/test/resources/tests/TestData.xlsx
+++ b/src/test/resources/tests/TestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RohitFulzele\Desktop\RCS\Automation_Testing\Testing\Company_Portal_JP\src\test\resources\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B6B529-595E-4F11-888A-1A8B75C28EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5CEE68-CE5A-44DC-9578-C88767477154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{CC144977-ADCD-4BF3-8A7D-A4E16E90E56F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="7" activeTab="10" xr2:uid="{CC144977-ADCD-4BF3-8A7D-A4E16E90E56F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,16 @@
     <sheet name="Edit_Profile_Info" sheetId="3" r:id="rId3"/>
     <sheet name="Password_Update" sheetId="4" r:id="rId4"/>
     <sheet name="Post_A_Job" sheetId="5" r:id="rId5"/>
+    <sheet name="Job_Listing" sheetId="6" r:id="rId6"/>
+    <sheet name="Applied_Candidate" sheetId="7" r:id="rId7"/>
+    <sheet name="Admin_Add_Company" sheetId="9" r:id="rId8"/>
+    <sheet name="Admin_Company_List" sheetId="10" r:id="rId9"/>
+    <sheet name="Admin_Post_a_Job" sheetId="11" r:id="rId10"/>
+    <sheet name="Admin_Job_Listing" sheetId="12" r:id="rId11"/>
+    <sheet name="11" sheetId="8" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="212">
   <si>
     <t>Username</t>
   </si>
@@ -52,12 +60,6 @@
     <t>wdhxcbwqidhxbio</t>
   </si>
   <si>
-    <t>ABC Pvt Ltd</t>
-  </si>
-  <si>
-    <t>abc@example.com</t>
-  </si>
-  <si>
     <t>XYZ Pvt Ltd</t>
   </si>
   <si>
@@ -76,9 +78,6 @@
     <t>CompanyPassword</t>
   </si>
   <si>
-    <t>Test@12345</t>
-  </si>
-  <si>
     <t>Test Toyata Cars Ltd</t>
   </si>
   <si>
@@ -86,9 +85,6 @@
   </si>
   <si>
     <t>www.toyotabharat.com/</t>
-  </si>
-  <si>
-    <t>testtoyatacarsltd@outlook.com</t>
   </si>
   <si>
     <t>Software</t>
@@ -378,9 +374,6 @@
     <t>We are looking for an experienced managing director to oversee business operations and provide strategic leadership. The managing director's responsibilities include developing and implementing strategic plans and company policies, maintaining an open dialogue with stakeholders, and driving organizational success</t>
   </si>
   <si>
-    <t xml:space="preserve">Professional Development, Managing Director </t>
-  </si>
-  <si>
     <t xml:space="preserve">Managing Director </t>
   </si>
   <si>
@@ -393,18 +386,349 @@
     <t>Professional Development, Managing Director</t>
   </si>
   <si>
-    <t xml:space="preserve"> T Automation Engineer</t>
+    <t>Tech Solution Pvt Ltd</t>
+  </si>
+  <si>
+    <t>yocobik731@easipro.com</t>
+  </si>
+  <si>
+    <t>L01631KA2010PTC096843</t>
+  </si>
+  <si>
+    <t>Password@123</t>
+  </si>
+  <si>
+    <t>Search_Job_1</t>
+  </si>
+  <si>
+    <t>Search_Job_2</t>
+  </si>
+  <si>
+    <t>Search_Job_3</t>
+  </si>
+  <si>
+    <t>Search_Job_4</t>
+  </si>
+  <si>
+    <t>Search_Job_5</t>
+  </si>
+  <si>
+    <t>Automation Engineer</t>
+  </si>
+  <si>
+    <t>Deal management, Project Development</t>
+  </si>
+  <si>
+    <t>Project Developement</t>
+  </si>
+  <si>
+    <t>Deal management</t>
+  </si>
+  <si>
+    <t>Maha</t>
+  </si>
+  <si>
+    <t>Update Jobs</t>
+  </si>
+  <si>
+    <t>Automation Tester</t>
+  </si>
+  <si>
+    <t>Data_Chnage_1</t>
+  </si>
+  <si>
+    <t>Data Change_2</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>B.com</t>
+  </si>
+  <si>
+    <t>2 years</t>
+  </si>
+  <si>
+    <t>5 years</t>
+  </si>
+  <si>
+    <t>Filter_Data_1</t>
+  </si>
+  <si>
+    <t>Filter_Data_2</t>
+  </si>
+  <si>
+    <t>Search_Candidate_1</t>
+  </si>
+  <si>
+    <t>Jani</t>
+  </si>
+  <si>
+    <t>TechNova Solution</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.technova.com </t>
+  </si>
+  <si>
+    <t>TechNova Solution was founded to help business owner's succeed through cutting-edge Digital Transformation. We deliver end-to-end solutions through valuable strategy development, consulting services, and highly skilled engineering execution</t>
+  </si>
+  <si>
+    <t>DataSwift Services</t>
+  </si>
+  <si>
+    <t>www.DataSwift Services.co.in</t>
+  </si>
+  <si>
+    <t>www.technova.co.in</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>DataSwift Services was founded to help business owner's succeed through cutting-edge Digital Transformation. We deliver end-to-end solutions through valuable strategy development, consulting services, and highly skilled engineering execution.</t>
+  </si>
+  <si>
+    <t>InfoTrack Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.InfoTrackSystems.com                           </t>
+  </si>
+  <si>
+    <t>Media and News</t>
+  </si>
+  <si>
+    <t>InfoTrack Systems" was founded to help business owner's succeed through cutting-edge Digital Transformation. We deliver end-to-end solutions through valuable strategy development, consulting services, and highly skilled engineering execution</t>
+  </si>
+  <si>
+    <t>www.xolewih641macho3.com</t>
+  </si>
+  <si>
+    <t>ByteFlow Technologies</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>Advertising</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.ByteFlow Technologiesco.in </t>
+  </si>
+  <si>
+    <t>ByteFlow Technologies was founded to help business owner's succeed through cutting-edge Digital Transformation. We deliver end-to-end solutions through valuable strategy development, consulting services, and highly skilled engineering execution.</t>
+  </si>
+  <si>
+    <t>NeoDigit Enterprises</t>
+  </si>
+  <si>
+    <t>Lucknow</t>
+  </si>
+  <si>
+    <t>UttarPradesh</t>
+  </si>
+  <si>
+    <t>Food Processing</t>
+  </si>
+  <si>
+    <t>NeoDigit Enterprises.co.in</t>
+  </si>
+  <si>
+    <t>NeoDigit Enterprises was founded to help business owner's succeed through cutting-edge Digital Transformation. We deliver end-to-end solutions through valuable strategy development, consulting services, and highly skilled engineering execution</t>
+  </si>
+  <si>
+    <t>L12345KA2020PTC012345</t>
+  </si>
+  <si>
+    <t>L12345KA2020PTC012665</t>
+  </si>
+  <si>
+    <t>U12345KA2020PTC012345</t>
+  </si>
+  <si>
+    <t>J96345KA2020PTC012345</t>
+  </si>
+  <si>
+    <t>K12345KA2020PTC012345</t>
+  </si>
+  <si>
+    <t>Upload_Logo</t>
+  </si>
+  <si>
+    <t>Upload_Cover</t>
+  </si>
+  <si>
+    <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Test_Company_01.jpg</t>
+  </si>
+  <si>
+    <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Cover_01.jpg</t>
+  </si>
+  <si>
+    <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Test_Company_02.png</t>
+  </si>
+  <si>
+    <r>
+      <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Cover_02.</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>jpg</t>
+    </r>
+  </si>
+  <si>
+    <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Test_Company_03.png</t>
+  </si>
+  <si>
+    <r>
+      <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Cover_03.</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>jpg</t>
+    </r>
+  </si>
+  <si>
+    <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Test_Company_04.jpg</t>
+  </si>
+  <si>
+    <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Cover_04.jpg</t>
+  </si>
+  <si>
+    <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Test_Company_05.png</t>
+  </si>
+  <si>
+    <t>C:\\Users\\RohitFulzele\\Downloads\\Test_Company\\Cover_05.jpg</t>
+  </si>
+  <si>
+    <t>Company_Name_EData</t>
+  </si>
+  <si>
+    <t>CIN_Number_Edata</t>
+  </si>
+  <si>
+    <t>City_Edata</t>
+  </si>
+  <si>
+    <t>State_Edata</t>
+  </si>
+  <si>
+    <t>Country_Edata</t>
+  </si>
+  <si>
+    <t>Website_Edata</t>
+  </si>
+  <si>
+    <t>Email_Edata</t>
+  </si>
+  <si>
+    <t>Phone_Number_Edata</t>
+  </si>
+  <si>
+    <t>Foundation_Date_Edata</t>
+  </si>
+  <si>
+    <t>Industry_Edata</t>
+  </si>
+  <si>
+    <t>Social_Media_Edata</t>
+  </si>
+  <si>
+    <t>Description_Edata</t>
+  </si>
+  <si>
+    <t>www.DataSwiftServices.co.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.ByteFlowTechnologies.co.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.NeoDigitEnterprises.co.in </t>
+  </si>
+  <si>
+    <t>tl7z1@ptct.net</t>
+  </si>
+  <si>
+    <t>b73v8@ptct.net</t>
+  </si>
+  <si>
+    <t>o8jmd30@ptct.net</t>
+  </si>
+  <si>
+    <t>htlh71@ptct.net</t>
+  </si>
+  <si>
+    <t>Hr@NeoDigitEnterprise.com</t>
+  </si>
+  <si>
+    <t>Search_Compnay_1</t>
+  </si>
+  <si>
+    <t>Search_Compnay_2</t>
+  </si>
+  <si>
+    <t>Search_Compnay_3</t>
+  </si>
+  <si>
+    <t>Search_Compnay_4</t>
+  </si>
+  <si>
+    <t>Search_Compnay_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Update Company</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Tamilnadu</t>
+  </si>
+  <si>
+    <t>Medical</t>
+  </si>
+  <si>
+    <t>Data_Change_1</t>
+  </si>
+  <si>
+    <t>Company_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
     <numFmt numFmtId="165" formatCode="[$-14009]dd/mm/yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,16 +773,54 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF201A1E"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -466,12 +828,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -500,6 +877,36 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -825,10 +1232,10 @@
   <sheetData>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3">
         <v>9876543210</v>
@@ -890,48 +1297,679 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F4792B0-9FA7-469C-8BD7-5C88758841EF}">
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="255.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="P1" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="T1" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="U1" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="V1" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="W1" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="X1" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="28">
+        <v>12022025</v>
+      </c>
+      <c r="D2" s="29">
+        <v>28032025</v>
+      </c>
+      <c r="E2" s="28">
+        <v>2</v>
+      </c>
+      <c r="F2" s="28">
+        <v>3</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="28">
+        <v>250000</v>
+      </c>
+      <c r="N2" s="28">
+        <v>350000</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="T2" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="U2" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="V2" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="W2" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="X2" s="28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="28">
+        <v>12012025</v>
+      </c>
+      <c r="D3" s="29">
+        <v>12022025</v>
+      </c>
+      <c r="E3" s="28">
+        <v>3</v>
+      </c>
+      <c r="F3" s="28">
+        <v>4</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="M3" s="28">
+        <v>500000</v>
+      </c>
+      <c r="N3" s="28">
+        <v>650000</v>
+      </c>
+      <c r="O3" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P3" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="S3" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="T3" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="U3" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="V3" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="W3" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="X3" s="28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="28">
+        <v>21012025</v>
+      </c>
+      <c r="D4" s="28">
+        <v>21022025</v>
+      </c>
+      <c r="E4" s="28">
+        <v>4</v>
+      </c>
+      <c r="F4" s="28">
+        <v>5</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" s="28">
+        <v>650000</v>
+      </c>
+      <c r="N4" s="28">
+        <v>750000</v>
+      </c>
+      <c r="O4" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="P4" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="S4" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="T4" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="U4" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="V4" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="W4" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="X4" s="28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="28">
+        <v>1012025</v>
+      </c>
+      <c r="D5" s="32">
+        <v>2022025</v>
+      </c>
+      <c r="E5" s="28">
+        <v>5</v>
+      </c>
+      <c r="F5" s="28">
+        <v>6</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="M5" s="28">
+        <v>600000</v>
+      </c>
+      <c r="N5" s="28">
+        <v>700000</v>
+      </c>
+      <c r="O5" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P5" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="S5" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="T5" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="U5" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="V5" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="W5" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="28">
+        <v>2022025</v>
+      </c>
+      <c r="D6" s="33">
+        <v>2032025</v>
+      </c>
+      <c r="E6" s="28">
+        <v>6</v>
+      </c>
+      <c r="F6" s="28">
+        <v>7</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="M6" s="28">
+        <v>1200000</v>
+      </c>
+      <c r="N6" s="28">
+        <v>1500000</v>
+      </c>
+      <c r="O6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P6" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="R6" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="S6" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="T6" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="U6" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="V6" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="W6" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="X6" s="31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="N8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="O9" t="s">
+        <v>210</v>
+      </c>
+      <c r="P9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D9DE41-241E-4AA3-A683-A418B113131C}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24591FB-9B7C-45FF-9BBF-C2C141C82519}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCC4D200-84FB-4860-96B2-B8999C979A71}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1234567890</v>
+        <v>109</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{63A18CD4-364C-4E18-B2F1-A9188F26BC8A}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{9CDF5396-D01C-4514-BC00-FEFD763A6BC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -943,6 +1981,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="6" max="6" width="23.140625" customWidth="1"/>
     <col min="7" max="7" width="19.85546875" customWidth="1"/>
     <col min="8" max="8" width="13.140625" customWidth="1"/>
@@ -953,63 +1992,63 @@
   <sheetData>
     <row r="1" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>110</v>
       </c>
       <c r="H2" s="5">
         <v>8454778475</v>
@@ -1018,19 +2057,16 @@
         <v>110121995</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{19E619AE-6FBD-4AE6-86D2-D587D382B0E5}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1047,24 +2083,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1108,78 +2144,78 @@
   <sheetData>
     <row r="1" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="K1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="O1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="R1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="S1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="V1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="P1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>54</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B2">
         <v>12022025</v>
@@ -1194,22 +2230,22 @@
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L2">
         <v>250000</v>
@@ -1218,39 +2254,39 @@
         <v>350000</v>
       </c>
       <c r="N2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P2" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="Q2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="R2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="S2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="T2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="V2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="W2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B3">
         <v>12012025</v>
@@ -1265,63 +2301,63 @@
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3">
+        <v>500000</v>
+      </c>
+      <c r="M3">
+        <v>650000</v>
+      </c>
+      <c r="N3" t="s">
         <v>76</v>
       </c>
-      <c r="I3" t="s">
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>89</v>
+      </c>
+      <c r="R3" t="s">
         <v>77</v>
       </c>
-      <c r="J3" t="s">
+      <c r="S3" t="s">
         <v>78</v>
       </c>
-      <c r="K3" t="s">
+      <c r="T3" t="s">
         <v>79</v>
       </c>
-      <c r="L3">
-        <v>50000</v>
-      </c>
-      <c r="M3">
-        <v>65000</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="U3" t="s">
+        <v>74</v>
+      </c>
+      <c r="V3" t="s">
+        <v>75</v>
+      </c>
+      <c r="W3" t="s">
         <v>80</v>
-      </c>
-      <c r="O3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>93</v>
-      </c>
-      <c r="R3" t="s">
-        <v>81</v>
-      </c>
-      <c r="S3" t="s">
-        <v>82</v>
-      </c>
-      <c r="T3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U3" t="s">
-        <v>78</v>
-      </c>
-      <c r="V3" t="s">
-        <v>79</v>
-      </c>
-      <c r="W3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B4">
         <v>21012025</v>
@@ -1336,63 +2372,63 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G4" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" t="s">
         <v>87</v>
       </c>
-      <c r="H4" t="s">
+      <c r="L4">
+        <v>650000</v>
+      </c>
+      <c r="M4">
+        <v>750000</v>
+      </c>
+      <c r="N4" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="O4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" t="s">
         <v>90</v>
       </c>
-      <c r="K4" t="s">
+      <c r="Q4" t="s">
+        <v>90</v>
+      </c>
+      <c r="R4" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="L4">
-        <v>65000</v>
-      </c>
-      <c r="M4">
-        <v>75000</v>
-      </c>
-      <c r="N4" s="14" t="s">
+      <c r="S4" t="s">
         <v>92</v>
       </c>
-      <c r="O4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="T4" t="s">
+        <v>93</v>
+      </c>
+      <c r="U4" t="s">
+        <v>86</v>
+      </c>
+      <c r="V4" t="s">
+        <v>87</v>
+      </c>
+      <c r="W4" t="s">
         <v>94</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>94</v>
-      </c>
-      <c r="R4" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="S4" t="s">
-        <v>96</v>
-      </c>
-      <c r="T4" t="s">
-        <v>97</v>
-      </c>
-      <c r="U4" t="s">
-        <v>90</v>
-      </c>
-      <c r="V4" t="s">
-        <v>91</v>
-      </c>
-      <c r="W4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B5">
         <v>1012025</v>
@@ -1407,63 +2443,63 @@
         <v>6</v>
       </c>
       <c r="F5" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L5">
+        <v>600000</v>
+      </c>
+      <c r="M5">
+        <v>700000</v>
+      </c>
+      <c r="N5" t="s">
+        <v>76</v>
+      </c>
+      <c r="O5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q5" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" s="15" t="s">
+      <c r="R5" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="J5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="S5" t="s">
         <v>102</v>
       </c>
-      <c r="L5">
-        <v>60000</v>
-      </c>
-      <c r="M5">
-        <v>70000</v>
-      </c>
-      <c r="N5" t="s">
-        <v>80</v>
-      </c>
-      <c r="O5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="14" t="s">
+      <c r="T5" t="s">
+        <v>81</v>
+      </c>
+      <c r="U5" t="s">
+        <v>102</v>
+      </c>
+      <c r="V5" t="s">
+        <v>81</v>
+      </c>
+      <c r="W5" t="s">
         <v>103</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="R5" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="S5" t="s">
-        <v>106</v>
-      </c>
-      <c r="T5" t="s">
-        <v>85</v>
-      </c>
-      <c r="U5" t="s">
-        <v>106</v>
-      </c>
-      <c r="V5" t="s">
-        <v>85</v>
-      </c>
-      <c r="W5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B6">
         <v>2022025</v>
@@ -1478,62 +2514,657 @@
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J6" t="s">
-        <v>96</v>
-      </c>
-      <c r="K6" t="s">
-        <v>110</v>
+        <v>121</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>120</v>
       </c>
       <c r="L6">
-        <v>120000</v>
+        <v>1200000</v>
       </c>
       <c r="M6">
-        <v>150000</v>
+        <v>1500000</v>
       </c>
       <c r="N6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="S6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="T6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="U6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="W6" s="15" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F81C8007-F503-4F92-BBC3-16A6112E1792}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="19">
+        <v>45808</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD46D92-D48F-49B9-A3B7-BC48F7312C2F}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73355DD-98E2-4BB4-ACC6-F087FF44F469}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.42578125" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J2">
+        <v>9685478543</v>
+      </c>
+      <c r="K2" s="11">
+        <v>12052010</v>
+      </c>
+      <c r="L2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J3">
+        <v>9685478544</v>
+      </c>
+      <c r="K3" s="25">
+        <v>16062000</v>
+      </c>
+      <c r="L3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J4">
+        <v>9685478548</v>
+      </c>
+      <c r="K4" s="25">
+        <v>12092019</v>
+      </c>
+      <c r="L4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J5">
+        <v>9685478585</v>
+      </c>
+      <c r="K5" s="25">
+        <v>20091998</v>
+      </c>
+      <c r="L5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M5" t="s">
+        <v>152</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J6">
+        <v>9565452545</v>
+      </c>
+      <c r="K6" s="25">
+        <v>15031989</v>
+      </c>
+      <c r="L6" t="s">
+        <v>157</v>
+      </c>
+      <c r="M6" t="s">
+        <v>158</v>
+      </c>
+      <c r="N6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C7" s="23"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F8" s="15"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{608201DA-255F-4427-828F-A084E4D845DD}"/>
+    <hyperlink ref="I2" r:id="rId2" xr:uid="{3E870145-1F3A-4380-AF36-CBC9AFD18477}"/>
+    <hyperlink ref="M2" r:id="rId3" xr:uid="{0018E00B-BE11-4753-BDE8-93D8BC5D4823}"/>
+    <hyperlink ref="I3" r:id="rId4" xr:uid="{E1A38AA1-6E22-4E83-8AAA-F7CFCF7F3915}"/>
+    <hyperlink ref="I4" r:id="rId5" xr:uid="{3ABA3F3B-7538-4084-A1C5-FB9DA134C1C6}"/>
+    <hyperlink ref="H4" r:id="rId6" xr:uid="{19E254EA-0B45-4E33-80C5-6A6628D6ED8F}"/>
+    <hyperlink ref="M4" r:id="rId7" xr:uid="{782977C4-03C4-46A0-9F49-67F3D0199D16}"/>
+    <hyperlink ref="I5" r:id="rId8" xr:uid="{5CBFA14F-8A36-4757-BC5F-96D82CC1EDFA}"/>
+    <hyperlink ref="H3" r:id="rId9" xr:uid="{BA0D9848-4378-42D6-9E5F-749349A38124}"/>
+    <hyperlink ref="H5" r:id="rId10" xr:uid="{0C1385B1-C388-4ED3-A855-A6F71C006BD9}"/>
+    <hyperlink ref="H6" r:id="rId11" xr:uid="{1EF81D81-1FDF-4F9B-B314-39CB37B7DFE7}"/>
+    <hyperlink ref="I6" r:id="rId12" xr:uid="{A2D890F9-9C5C-4F71-BDC7-AD6452D5844E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15062A1A-0288-4F80-8694-EEA145356B49}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="20">
+        <v>7038799247</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>